--- a/output/第10期計画_アンケート調査の集計分析報告書.xlsx
+++ b/output/第10期計画_アンケート調査の集計分析報告書.xlsx
@@ -935,7 +935,7 @@
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>母集団・時点・回収状況の3点に留保がある。点検事項32件のうち重大5件は取扱いの決定を要する。</t>
+          <t>母集団・時点・回収状況の3点に留保がある。点検事項33件のうち重大5件は取扱いの決定を要する。</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -2654,7 +2654,7 @@
     <row r="20" ht="52" customHeight="1">
       <c r="A20" s="7" t="inlineStr">
         <is>
-          <t>注1）「必須」は、計画本文に数値を載せる際に必ず付す留保である。「決定待ち」は、点検事項の取扱いが決まるまで数値が確定しないものである。注2）本報告書では、「〜に由来する」「〜と整合する（根拠として）」「1件も〜ない」「有意差がないため関係がない」「全国トップ級」の5つの表現を用いない（別冊「主張の根拠水準の棚卸しと再レビュー」07シート）。注3）点検事項32件の全文は別冊「実施済み3調査の受領点検と集計」02シートによる。</t>
+          <t>注1）「必須」は、計画本文に数値を載せる際に必ず付す留保である。「決定待ち」は、点検事項の取扱いが決まるまで数値が確定しないものである。注2）本報告書では、「〜に由来する」「〜と整合する（根拠として）」「1件も〜ない」「有意差がないため関係がない」「全国トップ級」の5つの表現を用いない（別冊「主張の根拠水準の棚卸しと再レビュー」07シート）。注3）点検事項33件の全文は別冊「実施済み3調査の受領点検と集計」02シートによる。</t>
         </is>
       </c>
     </row>

--- a/output/第10期計画_アンケート調査の集計分析報告書.xlsx
+++ b/output/第10期計画_アンケート調査の集計分析報告書.xlsx
@@ -935,7 +935,7 @@
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>母集団・時点・回収状況の3点に留保がある。点検事項33件のうち重大5件は取扱いの決定を要する。</t>
+          <t>母集団・時点・回収状況の3点に留保がある。点検事項34件のうち重大5件は取扱いの決定を要する。</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>②は9施設が未回答である</t>
+          <t>②は13施設が未回答である（把握率58.1％）</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -2654,7 +2654,7 @@
     <row r="20" ht="52" customHeight="1">
       <c r="A20" s="7" t="inlineStr">
         <is>
-          <t>注1）「必須」は、計画本文に数値を載せる際に必ず付す留保である。「決定待ち」は、点検事項の取扱いが決まるまで数値が確定しないものである。注2）本報告書では、「〜に由来する」「〜と整合する（根拠として）」「1件も〜ない」「有意差がないため関係がない」「全国トップ級」の5つの表現を用いない（別冊「主張の根拠水準の棚卸しと再レビュー」07シート）。注3）点検事項33件の全文は別冊「実施済み3調査の受領点検と集計」02シートによる。</t>
+          <t>注1）「必須」は、計画本文に数値を載せる際に必ず付す留保である。「決定待ち」は、点検事項の取扱いが決まるまで数値が確定しないものである。注2）本報告書では、「〜に由来する」「〜と整合する（根拠として）」「1件も〜ない」「有意差がないため関係がない」「全国トップ級」の5つの表現を用いない（別冊「主張の根拠水準の棚卸しと再レビュー」07シート）。注3）点検事項34件の全文は別冊「実施済み3調査の受領点検と集計」02シートによる。</t>
         </is>
       </c>
     </row>
@@ -3886,7 +3886,7 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>9施設が未回答。うち8施設は介護保険外の住まいである（点検事項No.30・No.32）</t>
+          <t>13施設が未回答（把握率58.1％）。うち8施設は介護保険外の住まいである（点検事項No.30・No.32）</t>
         </is>
       </c>
     </row>
@@ -5450,7 +5450,7 @@
     <row r="2" ht="52" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>施設等票18件により、施設・居住系の入退所の実態を集計する。回答した18施設は区域内の施設・住まい26施設のうちの一部であり、定員は北海道の名簿による（06シート）。</t>
+          <t>施設等票18件により、施設・居住系の入退所の実態を集計する。回答した18施設は区域内の施設・住まい31施設のうちの一部であり（把握率58.1％）、定員は北海道の名簿による（06シート）。</t>
         </is>
       </c>
     </row>
@@ -6251,7 +6251,7 @@
     <row r="48" ht="78" customHeight="1">
       <c r="A48" s="7" t="inlineStr">
         <is>
-          <t>注1）本調査に回答したのは18施設であり、区域内の施設・住まい26施設のうち9施設が未回答である（06シート）。とくに区域内最大の特定施設（さわやか東神楽館・定員100人）が回答していないため、入所前の居場所・退去先の集計は定員56人分の2施設に基づく（点検事項No.32）。定員・入居者数・要介護度別の内訳・従業者数は介護サービス情報公表システムの個別画面（記入日 令和7年10月6日）により補うことができるが、入所前の居場所と退去先は公表されていない。注2）入所率は調査に回答した施設の定員に対するものである。区域内の定員は北海道の名簿による（06シート）。注3）区域内・区域外の別は、調査票の「市内／市外」の選択肢による。「市内」が町単位か広域連合単位かが定義されていないため、介護サービス自給率（δ）との接続には確認を要する（点検事項No.25）。</t>
+          <t>注1）本調査に回答したのは18施設であり、区域内の施設・住まい31施設のうち13施設が未回答である（把握率58.1％。06シート）。とくに区域内最大の特定施設（さわやか東神楽館・定員100人）が回答していないため、入所前の居場所・退去先の集計は定員56人分の2施設に基づく（点検事項No.32）。定員・入居者数・要介護度別の内訳・従業者数は介護サービス情報公表システムの個別画面（記入日 令和7年10月6日）により補うことができるが、入所前の居場所と退去先は公表されていない。注2）入所率は調査に回答した施設の定員に対するものである。区域内の定員は北海道の名簿による（06シート）。注3）区域内・区域外の別は、調査票の「市内／市外」の選択肢による。「市内」が町単位か広域連合単位かが定義されていないため、介護サービス自給率（δ）との接続には確認を要する（点検事項No.25）。</t>
         </is>
       </c>
     </row>

--- a/output/第10期計画_アンケート調査の集計分析報告書.xlsx
+++ b/output/第10期計画_アンケート調査の集計分析報告書.xlsx
@@ -1981,7 +1981,7 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>人数</t>
+          <t>推計人数</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
@@ -2004,7 +2004,7 @@
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>1013</v>
+        <v>1016</v>
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
@@ -2026,7 +2026,7 @@
         </is>
       </c>
       <c r="B11" s="8" t="n">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C11" s="8" t="inlineStr">
         <is>
@@ -2048,7 +2048,7 @@
         </is>
       </c>
       <c r="B12" s="8" t="n">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
@@ -2212,10 +2212,10 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="65" customHeight="1">
+    <row r="23" ht="91" customHeight="1">
       <c r="A23" s="7" t="inlineStr">
         <is>
-          <t>注1）見込量は別冊「将来推計 第2段階　サービス見込量」（8シート）による。利用率と1人当たりの利用日数・回数の置き方はヒアリングシート項目6でご意向を確認する事項であり、確定していない。注2）本シートは、4調査を横断したクロス集計に代えて調査相互を接続するものである（13シート）。個票を突き合わせたものではなく、集計値と供給構造による対照である。注3）「いずれも利用していない486人」と健康とくらしの調査の「介護・介助が必要だが受けていない7.0％」は母集団が異なる（前者は認定者、後者は一般高齢者）。合算も比率の比較もしない。</t>
+          <t>注1）見込量は別冊「将来推計 第2段階　サービス見込量」（8シート）による。利用率と1人当たりの利用日数・回数の置き方はヒアリングシート項目6でご意向を確認する事項であり、確定していない。注2）本シートは、4調査を横断したクロス集計に代えて調査相互を接続するものである（13シート）。個票を突き合わせたものではなく、集計値と供給構造による対照である。注3）人数は、認定者数1,984人（令和8年3月末）に令和7年度の合計利用率（見える化D45系列）を乗じて算定した推計人数であり、月平均の受給者実績（在宅1,013人・居住系144人・施設336人）とは算定の方法が異なるため一致しない。4区分の合計は1,984人となる。注4）「いずれも利用していない486人」と健康とくらしの調査の「介護・介助が必要だが受けていない7.0％」は母集団が異なる（前者は認定者、後者は一般高齢者）。合算も比率の比較もしない。</t>
         </is>
       </c>
     </row>
@@ -3283,12 +3283,12 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>特定施設の入居者は軽度者が7割である</t>
+          <t>【参考・時点混在】特定施設の入居者の要介護度構成</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>さわやか東神楽館（定員100人・入居者97人）の要介護度は要支援1・2が26人（26.8％）、要介護1が42人（43.3％）で、要支援1〜要介護1が68人（70.1％）を占める。要介護4・5は9人（9.3％）にとどまる。</t>
+          <t>さわやか東神楽館（定員100人・入居者97人・令和7年10月6日現在）の要介護度は要支援1・2が26人（26.8％）、要介護1が42人（43.3％）で、要支援1〜要介護1が68人（70.1％）を占める。要介護4・5は9人（9.3％）にとどまる。調査に回答した2施設（57人・令和7年4月1日現在）と合算すると要支援1〜要介護2は110人／154人（71.4％）となるが、回答2施設のみでは30人／57人（52.6％）であり、時点と施設構成に強く左右される。同一時点の3施設のデータへ更新するまで、整備の必要量の算定には使用しない。</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
@@ -3299,12 +3299,12 @@
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>なし</t>
-        </is>
-      </c>
-      <c r="F23" s="21" t="inlineStr">
-        <is>
-          <t>着手可</t>
+          <t>同一時点の3施設データ</t>
+        </is>
+      </c>
+      <c r="F23" s="14" t="inlineStr">
+        <is>
+          <t>決定待ち</t>
         </is>
       </c>
     </row>
@@ -3377,7 +3377,7 @@
         </is>
       </c>
       <c r="B28" s="8" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
@@ -3399,7 +3399,7 @@
         </is>
       </c>
       <c r="B29" s="8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
@@ -3417,7 +3417,7 @@
     <row r="31" ht="39" customHeight="1">
       <c r="A31" s="7" t="inlineStr">
         <is>
-          <t>注1）所見20件のうち12件は点検事項の取扱いの決定を要せず着手できる。注2）反映先は計画素案（第10稿）の章節による。実際の反映は別管理表で管理し、計画本文には確認事項の注記を書かない。注3）本シートの所見は受託者によるものであり、計画本文への反映は発注者のご意向を確認したうえで行う。</t>
+          <t>注1）所見20件のうち11件は点検事項の取扱いの決定を要せず着手できる。注2）反映先は計画素案（第10稿）の章節による。実際の反映は別管理表で管理し、計画本文には確認事項の注記を書かない。注3）本シートの所見は受託者によるものであり、計画本文への反映は発注者のご意向を確認したうえで行う。</t>
         </is>
       </c>
     </row>
@@ -6244,7 +6244,7 @@
       <c r="E46" s="12" t="inlineStr"/>
       <c r="F46" s="12" t="inlineStr">
         <is>
-          <t>軽度者が7割を占める。特定施設が重度者の受け皿として機能しているとは限らない。要支援者が26人入居しており、居住系の見込量を要介護度別に置く際に要支援を無視できない</t>
+          <t>【参考】本施設では軽度者が7割を占める。特定施設が重度者の受け皿として機能しているとは限らない。要支援者が26人入居しており、居住系の見込量を要介護度別に置く際に要支援を無視できない。1施設の値であり、区域内3施設の構成を示すものではない</t>
         </is>
       </c>
     </row>

--- a/output/第10期計画_アンケート調査の集計分析報告書.xlsx
+++ b/output/第10期計画_アンケート調査の集計分析報告書.xlsx
@@ -935,7 +935,7 @@
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>母集団・時点・回収状況の3点に留保がある。点検事項34件のうち重大5件は取扱いの決定を要する。</t>
+          <t>母集団・時点・回収状況の3点に留保がある。点検事項35件のうち重大6件は取扱いの決定を要する。</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -960,7 +960,7 @@
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>所見20件。うち着手可11件、重大5件の決定待ち9件。</t>
+          <t>所見20件。うち着手可11件、重大6件の決定待ち9件。</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -2081,7 +2081,7 @@
       <c r="E13" s="9" t="n"/>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>認定者1,984人の4分の1。健康とくらしの調査の「介護・介助が必要だが受けていない7.0％」とは別の集団であり、合算しない。内訳（資料依頼No.7）の受領後に要因を分解する</t>
+          <t>認定者1,984人の4分の1。健康とくらしの調査の「介護・介助が必要だが受けていない7.0％」とは別の集団であり、合算しない。内訳（資料依頼No.8）の受領後に要因を分解する</t>
         </is>
       </c>
     </row>
@@ -2654,7 +2654,7 @@
     <row r="20" ht="52" customHeight="1">
       <c r="A20" s="7" t="inlineStr">
         <is>
-          <t>注1）「必須」は、計画本文に数値を載せる際に必ず付す留保である。「決定待ち」は、点検事項の取扱いが決まるまで数値が確定しないものである。注2）本報告書では、「〜に由来する」「〜と整合する（根拠として）」「1件も〜ない」「有意差がないため関係がない」「全国トップ級」の5つの表現を用いない（別冊「主張の根拠水準の棚卸しと再レビュー」07シート）。注3）点検事項34件の全文は別冊「実施済み3調査の受領点検と集計」02シートによる。</t>
+          <t>注1）「必須」は、計画本文に数値を載せる際に必ず付す留保である。「決定待ち」は、点検事項の取扱いが決まるまで数値が確定しないものである。注2）本報告書では、「〜に由来する」「〜と整合する（根拠として）」「1件も〜ない」「有意差がないため関係がない」「全国トップ級」の5つの表現を用いない（別冊「主張の根拠水準の棚卸しと再レビュー」07シート）。注3）点検事項35件の全文は別冊「実施済み3調査の受領点検と集計」02シートによる。</t>
         </is>
       </c>
     </row>
@@ -7741,7 +7741,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>東神楽町アゼリアハイツ（50人）が調査に未回答。定員160人は資料依頼No.6③の「定員減少234人→160人」と一致する</t>
+          <t>東神楽町アゼリアハイツ（50人）が調査に未回答。定員160人は資料依頼No.7③の「定員減少234人→160人」と一致する</t>
         </is>
       </c>
     </row>

--- a/output/第10期計画_アンケート調査の集計分析報告書.xlsx
+++ b/output/第10期計画_アンケート調査の集計分析報告書.xlsx
@@ -21,6 +21,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11_調査結果の限界と留保" sheetId="12" state="visible" r:id="rId12"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12_主要所見と計画本文への反映" sheetId="13" state="visible" r:id="rId13"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="13_横断クロス集計を行わないことの整理" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="14_公表データによる補完と留保の解消" sheetId="15" state="visible" r:id="rId15"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -618,7 +619,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E26"/>
+  <dimension ref="A1:E27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -994,113 +995,111 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="18" customHeight="1">
-      <c r="A19" s="6" t="inlineStr">
+    <row r="18" ht="52" customHeight="1">
+      <c r="A18" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>14_公表データによる補完と留保の解消</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>11シートの留保のうち、その後に取得した公表データ及び外部統計により解消したもの・しなかったものを整理する。</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>解消6件・未解消4件・一部解消1件・公表待ち1件・決定待ち1件。訪問介護13事業所181人の全数把握により、訪問系の代表性の留保が解消した。</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>更新の記録</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="18" customHeight="1">
+      <c r="A20" s="6" t="inlineStr">
         <is>
           <t>【4調査の位置づけ】</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="30" customHeight="1">
-      <c r="A20" s="3" t="inlineStr">
+    <row r="21" ht="30" customHeight="1">
+      <c r="A21" s="3" t="inlineStr">
         <is>
           <t>調査</t>
         </is>
       </c>
-      <c r="B20" s="3" t="inlineStr">
+      <c r="B21" s="3" t="inlineStr">
         <is>
           <t>対象</t>
         </is>
       </c>
-      <c r="C20" s="3" t="inlineStr">
+      <c r="C21" s="3" t="inlineStr">
         <is>
           <t>把握するもの</t>
         </is>
       </c>
-      <c r="D20" s="3" t="inlineStr">
+      <c r="D21" s="3" t="inlineStr">
         <is>
           <t>計画での用途</t>
         </is>
       </c>
-      <c r="E20" s="3" t="inlineStr">
+      <c r="E21" s="3" t="inlineStr">
         <is>
           <t>実施時期</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="48" customHeight="1">
-      <c r="A21" s="5" t="inlineStr">
-        <is>
-          <t>① 在宅生活改善調査</t>
-        </is>
-      </c>
-      <c r="B21" s="5" t="inlineStr">
-        <is>
-          <t>居宅介護支援事業所・小規模多機能・地域包括の利用者（要介護者本人・家族）</t>
-        </is>
-      </c>
-      <c r="C21" s="5" t="inlineStr">
-        <is>
-          <t>在宅生活の継続を困難にしている要因、必要な生活支援、より適切と思われるサービス</t>
-        </is>
-      </c>
-      <c r="D21" s="5" t="inlineStr">
-        <is>
-          <t>第2章第4節、第5章基本目標2、代表KPI H06</t>
-        </is>
-      </c>
-      <c r="E21" s="4" t="inlineStr">
-        <is>
-          <t>令和7年度</t>
         </is>
       </c>
     </row>
     <row r="22" ht="48" customHeight="1">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>② 居所変更実態調査</t>
+          <t>① 在宅生活改善調査</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>施設・居住系の事業所</t>
+          <t>居宅介護支援事業所・小規模多機能・地域包括の利用者（要介護者本人・家族）</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>入所前の居場所、退去先、退去理由、待機者、受入可能な医療処置</t>
+          <t>在宅生活の継続を困難にしている要因、必要な生活支援、より適切と思われるサービス</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>第2章第6節、第6章第2節・第4節・第5節、代表KPI H11</t>
+          <t>第2章第4節、第5章基本目標2、代表KPI H06</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>令和7年4月1日現在</t>
+          <t>令和7年度</t>
         </is>
       </c>
     </row>
     <row r="23" ht="48" customHeight="1">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>③ 介護人材実態調査</t>
+          <t>② 居所変更実態調査</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>介護サービス事業所とその職員</t>
+          <t>施設・居住系の事業所</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>介護職員数、資格、雇用形態、勤続年数、採用・離職、外国人職員</t>
+          <t>入所前の居場所、退去先、退去理由、待機者、受入可能な医療処置</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>第3章第5節、第5章基本目標4、代表KPI H13・H14</t>
+          <t>第2章第6節、第6章第2節・第4節・第5節、代表KPI H11</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr">
@@ -1112,32 +1111,59 @@
     <row r="24" ht="48" customHeight="1">
       <c r="A24" s="5" t="inlineStr">
         <is>
+          <t>③ 介護人材実態調査</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>介護サービス事業所とその職員</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>介護職員数、資格、雇用形態、勤続年数、採用・離職、外国人職員</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t>第3章第5節、第5章基本目標4、代表KPI H13・H14</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>令和7年4月1日現在</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="48" customHeight="1">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
           <t>④ 健康とくらしの調査</t>
         </is>
       </c>
-      <c r="B24" s="5" t="inlineStr">
+      <c r="B25" s="5" t="inlineStr">
         <is>
           <t>65歳以上の一般高齢者及び総合事業対象者（要支援・要介護認定者を含まない）</t>
         </is>
       </c>
-      <c r="C24" s="5" t="inlineStr">
+      <c r="C25" s="5" t="inlineStr">
         <is>
           <t>フレイル、社会参加、閉じこもり、うつ、IADL、生活支援ニーズ</t>
         </is>
       </c>
-      <c r="D24" s="5" t="inlineStr">
+      <c r="D25" s="5" t="inlineStr">
         <is>
           <t>第2章第4節、第5章基本目標1、代表KPI H04・H05</t>
         </is>
       </c>
-      <c r="E24" s="4" t="inlineStr">
+      <c r="E25" s="4" t="inlineStr">
         <is>
           <t>令和7年11月17日〜12月8日</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="78" customHeight="1">
-      <c r="A26" s="7" t="inlineStr">
+    <row r="27" ht="78" customHeight="1">
+      <c r="A27" s="7" t="inlineStr">
         <is>
           <t>注1）本報告書は受託者による集計・分析の結果であり、計画本文への反映は発注者のご意向を確認したうえで行う。注2）個票データ（在宅生活改善調査の利用者票99票、介護人材実態調査の職員個票317人、健康とくらしの調査の個票4,729票）は個人情報を含むため、成果品には集計値のみを収録する。注3）本報告書の点検の詳細は別冊「実施済み3調査の受領点検と集計」（16シート）による。④の詳細は別冊「調査クロス集計・分析」（24シート）による。注4）本報告書は令和8年8月5日現在である。点検事項の取扱いの決定により数値が変わる箇所は11シート及び12シートに示す。</t>
         </is>
@@ -1146,8 +1172,8 @@
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A26:E26"/>
-    <mergeCell ref="A19:E19"/>
+    <mergeCell ref="A27:E27"/>
+    <mergeCell ref="A20:E20"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3726,6 +3752,525 @@
   <mergeCells count="2">
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="A15:E15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F23"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>公表データによる補完と、留保の解消の状況</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="52" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>本報告書の11シートに掲げた留保のうち、その後に取得した公表データ及び外部統計により解消したもの、及び解消しなかったものを整理する。計画本文に用いる数値の確からしさを更新するためのものである。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>【1　解消した留保】</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>No.</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>留保の内容</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>補完に用いたデータ</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>解消の内容</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>計画本文への反映</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>状態</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="88" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>訪問系は13事業所のうち3事業所からの回答であり、区域全体を代表しない（11シートNo.3・No.5）</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>介護サービス情報公表システムの個別公表画面（13事業所）</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>訪問介護13事業所すべての訪問介護員等の実人数を把握した。実人数181人で、調査回答分42人の約4.3倍である。調査と公表画面の双方がある3事業所のうち2事業所は実人数が完全に一致しており、公表画面の値は調査と同じ水準で扱える。</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>第2章第6節に全数把握の表を追加した</t>
+        </is>
+      </c>
+      <c r="F6" s="21" t="inlineStr">
+        <is>
+          <t>解消</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="88" customHeight="1">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>訪問介護の担い手の構造が把握できない</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>同上（事業所の所在する建物の記載）</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>13事業所のうち8事業所（訪問介護員等128人・70.7％、利用者225人・65.0％）が住宅型有料老人ホーム、サービス付き高齢者向け住宅又は介護付有料老人ホームに併設されていることが確認できた。併設のない事業所は5事業所（53人）である。</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>第2章第6節。住まいの整備方針と訪問介護の供給力が一体であることの根拠</t>
+        </is>
+      </c>
+      <c r="F7" s="21" t="inlineStr">
+        <is>
+          <t>解消</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="88" customHeight="1">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>訪問系の人材の動きが把握できない</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>同上（前年度の採用者数・退職者数）</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>前年度の採用23人・退職28人で、退職が5人上回る。退職が採用を上回る事業所は13事業所中5事業所である。</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>第2章第6節、第5章 基本目標4</t>
+        </is>
+      </c>
+      <c r="F8" s="21" t="inlineStr">
+        <is>
+          <t>解消</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="88" customHeight="1">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>④健康とくらしの調査の世帯構成が国勢調査の世帯類型と対応しない（11シートNo.1）</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>国勢調査（令和2年・令和7年速報）、見える化A5〜A8、在宅生活改善調査</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>3つの出所を対照し、水準（美瑛町が高い）と増加の速さ（東神楽町が速い）が別であることを確認した。高齢者単身世帯の10年増加率は東神楽町＋73.6％・東川町＋66.1％・美瑛町＋34.5％である。</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>第2章第1節の世帯の記述を是正した</t>
+        </is>
+      </c>
+      <c r="F9" s="21" t="inlineStr">
+        <is>
+          <t>解消</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="88" customHeight="1">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>H12（必要サービス未充足率）のデータ源がない</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>①在宅生活改善調査 問3（本報告書02シート）</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>区域内に事業所が存在しない4サービスを「より適切と思われるサービス」として選んだ票は98票中20票（20.4％）である。H12の代理指標として定義できる。</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>第4章第3節・資料1のH12</t>
+        </is>
+      </c>
+      <c r="F10" s="21" t="inlineStr">
+        <is>
+          <t>解消</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="88" customHeight="1">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>H07・H08のデータ源がない（在宅介護実態調査を未実施）</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>④健康とくらしの調査 サブコア1【問17】4）及び【大雪－問4】1）</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>主に介護をしている者の割合3.4％（n=2,217）、世話をしてくれる人がいない者の割合8.7％（n=4,599）。いずれも代理指標として算定できる。</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>第4章第3節・資料1のH07・H08</t>
+        </is>
+      </c>
+      <c r="F11" s="21" t="inlineStr">
+        <is>
+          <t>解消</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="39" customHeight="1">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>注1）本シートの「解消」は、留保が完全になくなったことを意味しない。No.1〜No.3は公表画面の記入日が事業所により異なり、1事業所は常勤換算数及び1人当たりの月間サービス提供時間が0と記入されている（記入漏れとみて集計に用いていない）。注2）No.5・No.6は代理指標であり、測るものが当初の定義から変わっている。指標名の改称を伴う。</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="18" customHeight="1">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>【2　解消しなかった留保】</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="30" customHeight="1">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>No.</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>留保の内容</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>なぜ解消しないか</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>必要なもの</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>計画本文での扱い</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>状態</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="76" customHeight="1">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>①利用者票は課題のある利用者を抽出する設計である（11シートNo.2）</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>調査の設計そのものに由来する。母集団が「在宅生活の維持が難しい利用者」であり、区域内の在宅利用者全体ではない。</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>解消できない。第11期に向けて設計の見直しを提案する</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>「調査対象となった99人のうち」と明記する。H12の20.4％も同じ留保が付く</t>
+        </is>
+      </c>
+      <c r="F16" s="22" t="inlineStr">
+        <is>
+          <t>未解消</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="76" customHeight="1">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>②居所変更実態調査は18施設からの回答である</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>区域内の住替え全体を母集団としていない。在宅から在宅への住替えが含まれない。</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>解消できない</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>施設側からみた住替えとして記述する</t>
+        </is>
+      </c>
+      <c r="F17" s="22" t="inlineStr">
+        <is>
+          <t>未解消</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="76" customHeight="1">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>①②③は配布数の記録がなく回収率を算定できない</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>配布の記録がないため事後に算定できない。訪問介護13事業所・居宅介護支援13事業所については公表データで母数を置き換えられる。</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>解消できない（訪問介護を除く）</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>母数を置き換えられるもののみ回収率を示す</t>
+        </is>
+      </c>
+      <c r="F18" s="14" t="inlineStr">
+        <is>
+          <t>一部解消</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="76" customHeight="1">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>令和7年国勢調査の世帯の家族類型が未公表である</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>人口等基本集計の公表が令和8年11月頃の見込みである。</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>令和7年国勢調査 人口等基本集計</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>令和2年国勢調査による。公表後に更新する旨を注記した</t>
+        </is>
+      </c>
+      <c r="F19" s="14" t="inlineStr">
+        <is>
+          <t>公表待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="76" customHeight="1">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>介護老人保健施設の介護職員数が見える化システムと一致しない</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>「介護職員」の範囲の解釈が確認できていない。調査77人に対し見える化は令和6年度59人である。</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>職種の範囲の定義の確認</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>［要確認］として注記を残す</t>
+        </is>
+      </c>
+      <c r="F20" s="22" t="inlineStr">
+        <is>
+          <t>未解消</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="76" customHeight="1">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>同一法人が施設・通所系と訪問系の両方に同一の職員13人を記入している</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>個票の突合により重複は特定したが、総数をどちらに計上するかの決定を要する。</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>総数の取扱いの決定</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>［要確認］として注記を残す</t>
+        </is>
+      </c>
+      <c r="F21" s="14" t="inlineStr">
+        <is>
+          <t>決定待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="39" customHeight="1">
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t>注3）留保No.7は本報告書で最も重い留保である。①在宅生活改善調査から算定するH12（20.4％）は第10期の代表KPIに用いる案としているが、母集団が抽出であることを指標の定義に明記する必要がある。注4）本シートは、公表データの取得により報告書作成時点から変わった部分を記録するものである。報告書の本体（02〜13シート）の数値は変更していない。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A14:F14"/>
+    <mergeCell ref="A23:F23"/>
+    <mergeCell ref="A12:F12"/>
+    <mergeCell ref="A4:F4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/第10期計画_アンケート調査の集計分析報告書.xlsx
+++ b/output/第10期計画_アンケート調査の集計分析報告書.xlsx
@@ -2643,7 +2643,7 @@
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>10シートの記述は「〜と整合する」「〜の背景にある」にとどめ、「〜に由来する」と書かない。</t>
+          <t>10シートの記述は「〜と符合する」「〜の背景にある」にとどめ、「〜に由来する」と書かない。</t>
         </is>
       </c>
       <c r="E17" s="14" t="inlineStr">
@@ -3443,7 +3443,7 @@
     <row r="31" ht="39" customHeight="1">
       <c r="A31" s="7" t="inlineStr">
         <is>
-          <t>注1）所見20件のうち11件は点検事項の取扱いの決定を要せず着手できる。注2）反映先は計画素案（第10稿）の章節による。実際の反映は別管理表で管理し、計画本文には確認事項の注記を書かない。注3）本シートの所見は受託者によるものであり、計画本文への反映は発注者のご意向を確認したうえで行う。</t>
+          <t>注1）所見20件のうち11件は点検事項の取扱いの決定を要せず着手できる。注2）反映先は計画素案の章節による。実際の反映は別管理表で管理し、計画本文には確認事項の注記を書かない。注3）本シートの所見は受託者によるものであり、計画本文への反映は発注者のご意向を確認したうえで行う。</t>
         </is>
       </c>
     </row>
@@ -4078,7 +4078,7 @@
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>調査の設計そのものに由来する。母集団が「在宅生活の維持が難しい利用者」であり、区域内の在宅利用者全体ではない。</t>
+          <t>調査の設計そのものによるものである。母集団が「在宅生活の維持が難しい利用者」であり、区域内の在宅利用者全体ではない。</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
@@ -4784,7 +4784,7 @@
       <c r="E12" s="9" t="n"/>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>最多。移動の確保が在宅生活の継続の鍵である。健康とくらしの調査でも自力移動の手段がない層が20％台であることと整合する</t>
+          <t>最多。移動の確保が在宅生活の継続の鍵である。健康とくらしの調査でも自力移動の手段がない層が20％台であることと符合する</t>
         </is>
       </c>
     </row>
@@ -9430,7 +9430,7 @@
     <row r="2" ht="52" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>区域内の実75事業所を運営する28法人の分布を見る。調査結果の偏りが、調査設計ではなく供給構造に由来することを示す。</t>
+          <t>区域内の実75事業所を運営する28法人の分布を見る。調査結果の偏りが、調査設計によるものか供給構造によるものかを分けて示す。</t>
         </is>
       </c>
     </row>
@@ -10009,7 +10009,7 @@
     <row r="31" ht="52" customHeight="1">
       <c r="A31" s="7" t="inlineStr">
         <is>
-          <t>注1）本シートは、調査結果の偏りが調査設計に由来するのか供給構造に由来するのかを分けて示すためのものである。偏りの存在は調査の欠陥を意味しない。注2）法人の集中は、①事業者の撤退が地域のサービス供給に与える影響が大きいこと、②事業所間の比較による質の評価が成り立ちにくいことを意味する。第6章第4節（整備の方針）の留意事項とする。注3）本シートの解釈は受託者によるものであり、計画本文に記述する場合は表現をご確認いただく。特定の法人の評価と受け取られない書き方とする。</t>
+          <t>注1）本シートは、調査結果の偏りが調査設計によるものか供給構造によるものかを分けて示すためのものである。偏りの存在は調査の欠陥を意味しない。注2）法人の集中は、①事業者の撤退が地域のサービス供給に与える影響が大きいこと、②事業所間の比較による質の評価が成り立ちにくいことを意味する。第6章第4節（整備の方針）の留意事項とする。注3）本シートの解釈は受託者によるものであり、計画本文に記述する場合は表現をご確認いただく。特定の法人の評価と受け取られない書き方とする。</t>
         </is>
       </c>
     </row>

--- a/output/第10期計画_アンケート調査の集計分析報告書.xlsx
+++ b/output/第10期計画_アンケート調査の集計分析報告書.xlsx
@@ -2680,7 +2680,7 @@
     <row r="20" ht="52" customHeight="1">
       <c r="A20" s="7" t="inlineStr">
         <is>
-          <t>注1）「必須」は、計画本文に数値を載せる際に必ず付す留保である。「決定待ち」は、点検事項の取扱いが決まるまで数値が確定しないものである。注2）本報告書では、「〜に由来する」「〜と整合する（根拠として）」「1件も〜ない」「有意差がないため関係がない」「全国トップ級」の5つの表現を用いない（別冊「主張の根拠水準の棚卸しと再レビュー」07シート）。注3）点検事項35件の全文は別冊「実施済み3調査の受領点検と集計」02シートによる。</t>
+          <t>注1）「必須」は、計画本文に数値を載せる際に必ず付す留保である。「決定待ち」は、点検事項の取扱いが決まるまで数値が確定しないものである。注2）本報告書では、「〜に由来する」「〜と整合する（根拠として）」「1件も〜ない」「有意差がないため関係がない」「全国トップ級」の5つの表現を用いない（受託者の自己点検（記述ルール））。注3）点検事項35件の全文は別冊「実施済み3調査の受領点検と集計」02シートによる。</t>
         </is>
       </c>
     </row>

--- a/output/第10期計画_アンケート調査の集計分析報告書.xlsx
+++ b/output/第10期計画_アンケート調査の集計分析報告書.xlsx
@@ -4416,12 +4416,12 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>介護保険の指定施設14＋介護保険外の住まい12＝26</t>
+          <t>介護保険の指定施設19＋介護保険外の住まい12＝31</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>指定施設13・介護保険外4（1件は種別不明）</t>
+          <t>指定施設14・介護保険外4</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
@@ -4431,7 +4431,7 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>13施設が未回答（把握率58.1％）。うち8施設は介護保険外の住まいである（点検事項No.30・No.32）</t>
+          <t>13施設が未回答（指定5・指定外8。把握率58.1％）。うち8施設は介護保険外の住まいである（点検事項No.30・No.32・No.34）</t>
         </is>
       </c>
     </row>
